--- a/Assets/FPS/Scripts/RegistersPerPillar/Obstacle.xlsx
+++ b/Assets/FPS/Scripts/RegistersPerPillar/Obstacle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juanes\adaptative_microgame\Assets\FPS\Scripts\RegistersPerPillar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5457020-1310-4E6F-ACF9-E56743B0F923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A365A27A-2769-4D45-85CB-0B5597261F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="10" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28665" yWindow="2085" windowWidth="20760" windowHeight="11790" firstSheet="10" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AlexVargas" sheetId="1" r:id="rId1"/>
@@ -290,7 +290,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
